--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/observations-summary.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="33">
   <si>
     <t>Profile</t>
   </si>
@@ -99,6 +99,18 @@
   </si>
   <si>
     <t>Quantity</t>
+  </si>
+  <si>
+    <t>tddui-observation-repas</t>
+  </si>
+  <si>
+    <t>TDDUI Observation Repas</t>
+  </si>
+  <si>
+    <t>TDDUI Observation Type#REPAS</t>
+  </si>
+  <si>
+    <t>dateTime</t>
   </si>
 </sst>
 </file>
@@ -232,7 +244,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -480,6 +492,41 @@
         <v>13</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K8" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
